--- a/Result/profitability/6865.xlsx
+++ b/Result/profitability/6865.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM23"/>
+  <dimension ref="A1:AM24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3351,6 +3351,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6865</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>68</v>
+      </c>
+      <c r="D24" t="n">
+        <v>33</v>
+      </c>
+      <c r="E24" t="n">
+        <v>34</v>
+      </c>
+      <c r="F24" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-2.76%</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="N24" t="n">
+        <v>41.615</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.7400000000000001</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.6607142857142858</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.4399092970521541</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>-1.584615384615385</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>10.23999999999999</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.252465483234714</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK24" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
